--- a/docs/baseline/02_Function_Definition.xlsx
+++ b/docs/baseline/02_Function_Definition.xlsx
@@ -589,7 +589,7 @@
         <x:v>문서 버전</x:v>
       </x:c>
       <x:c r="F3" s="23" t="str">
-        <x:v>v1.2</x:v>
+        <x:v>v2.0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" hidden="0" customHeight="1">
@@ -597,13 +597,13 @@
         <x:v>기준일</x:v>
       </x:c>
       <x:c r="B4" s="23" t="str">
-        <x:v>2026-09-03</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
         <x:v>기준선 ID</x:v>
       </x:c>
       <x:c r="D4" s="23" t="str">
-        <x:v>HC-RSV-RCP-20260903-R2</x:v>
+        <x:v>HC-RSV-RCP-20260904-R3</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
         <x:v>논리 기능</x:v>
@@ -655,7 +655,7 @@
     <x:row r="7" ht="34" customHeight="1"/>
     <x:row r="8" ht="34" hidden="0" customHeight="1">
       <x:c r="A8" s="30" t="str">
-        <x:v>최종 판정: 정책 ↔ 프로세스 ↔ 기능 ↔ Rule ↔ UI ↔ DB 추적에 구조적 결함이 없으며, 본 파일은 HC-RSV-RCP-20260903-R2 기준선의 최종 기능계약으로 이후 READ-ONLY로 사용한다.</x:v>
+        <x:v>최종 판정: 정책 ↔ 프로세스 ↔ 기능 ↔ Rule ↔ UI ↔ DB 추적에 구조적 결함이 없으며, 본 파일은 HC-RSV-RCP-20260904-R3 기준선의 최종 기능계약으로 이후 READ-ONLY로 사용한다.</x:v>
       </x:c>
       <x:c r="B8" s="30"/>
       <x:c r="C8" s="30"/>
@@ -1358,7 +1358,7 @@
         <x:v>예약 취소 처리</x:v>
       </x:c>
       <x:c r="G25" s="36" t="str">
-        <x:v>현재 상태가 예약(RSV)인 업무만 동일 행을 취소(CNL)로 변경한다. 물리삭제·복원은 하지 않으며 재진행은 신규예약으로 처리한다.</x:v>
+        <x:v>현재 상태가 예약(RSV)인 업무만 동일 행을 예약취소(CNR)로 변경한다. 물리삭제·복원은 하지 않으며 재진행은 신규예약으로 처리한다.</x:v>
       </x:c>
       <x:c r="H25" s="36" t="str">
         <x:v>P02-07</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>접수 대상 예약 확인</x:v>
       </x:c>
       <x:c r="G27" s="36" t="str">
-        <x:v>확정 PatientId의 당일 취소되지 않은 업무를 조회한다. 예약(RSV)은 접수 대상으로 사용하고 접수완료(RCP)는 재접수를 차단하며 취소(CNL)는 제외한다.</x:v>
+        <x:v>확정 PatientId의 당일 취소되지 않은 업무를 조회한다. 예약(RSV)은 접수 대상으로 사용하고 접수완료(RCP)는 재접수를 차단하며 취소(CNR·CNC)는 제외한다.</x:v>
       </x:c>
       <x:c r="H27" s="36" t="str">
         <x:v>P03-01~02</x:v>
@@ -1648,7 +1648,7 @@
         <x:v>접수 취소 처리</x:v>
       </x:c>
       <x:c r="G35" s="36" t="str">
-        <x:v>현재 상태가 접수완료(RCP)인 업무만 동일 행을 취소(CNL)로 변경한다. 예약 상태로 되돌리지 않으며 해당 업무 전체가 취소된 것으로 처리한다.</x:v>
+        <x:v>현재 상태가 접수완료(RCP)인 업무만 동일 행을 접수취소(CNC)로 변경한다. 예약 상태로 되돌리지 않으며 해당 업무 전체가 취소된 것으로 처리한다.</x:v>
       </x:c>
       <x:c r="H35" s="36" t="str">
         <x:v>P03-06</x:v>
@@ -1706,7 +1706,7 @@
         <x:v>상태별 내역 확인</x:v>
       </x:c>
       <x:c r="G37" s="36" t="str">
-        <x:v>예약(RSV), 접수완료(RCP), 취소(CNL)를 조회 대상으로 포함한다. 취소 건도 보존·조회하되 후속 변경 Action은 허용하지 않는다.</x:v>
+        <x:v>예약(RSV), 접수완료(RCP), 예약취소(CNR), 접수취소(CNC)를 조회 대상으로 포함한다. 취소 건도 보존·조회하되 후속 변경 Action은 허용하지 않는다.</x:v>
       </x:c>
       <x:c r="H37" s="36" t="str">
         <x:v>P02-05, P03-04</x:v>
@@ -1892,7 +1892,7 @@
         <x:v>일반건강검진 대상판정</x:v>
       </x:c>
       <x:c r="E5" s="36" t="str">
-        <x:v>예약일보다 과거인 일반건강검진 완료이력만 사용한다. RSV/RCP/CNL과 예약일 당일·이후 완료이력은 제외한다.</x:v>
+        <x:v>예약일보다 과거인 일반건강검진 완료이력만 사용한다. RSV/RCP/CNR/CNC와 예약일 당일·이후 완료이력은 제외한다.</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
         <x:v>F-COM-003</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>RP-07</x:v>
       </x:c>
       <x:c r="I5" s="36" t="str">
-        <x:v>HIS_GENERAL_CHECKUP_COMPLETIONS</x:v>
+        <x:v>완료이력</x:v>
       </x:c>
       <x:c r="J5" s="36" t="str">
         <x:v>최근 과거 1건</x:v>
@@ -2319,7 +2319,7 @@
         <x:v>EX010</x:v>
       </x:c>
       <x:c r="J18" s="36" t="str">
-        <x:v>INFO_PATIENT_EXAM_EXCLUSIONS</x:v>
+        <x:v>수검자.HepatitisBExcluded</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="46" hidden="0" customHeight="1">
@@ -2810,7 +2810,7 @@
         <x:v>RP-08, RCP-05</x:v>
       </x:c>
       <x:c r="I34" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORK_EXAMS</x:v>
+        <x:v>검사항목</x:v>
       </x:c>
       <x:c r="J34" s="36" t="str"/>
     </x:row>
@@ -2872,7 +2872,7 @@
         <x:v>CP-03</x:v>
       </x:c>
       <x:c r="I36" s="36" t="str">
-        <x:v>MST_HOLIDAYS</x:v>
+        <x:v>휴무일</x:v>
       </x:c>
       <x:c r="J36" s="36" t="str"/>
     </x:row>
@@ -2902,7 +2902,7 @@
         <x:v>CP-03</x:v>
       </x:c>
       <x:c r="I37" s="36" t="str">
-        <x:v>MST_HOLIDAYS</x:v>
+        <x:v>휴무일</x:v>
       </x:c>
       <x:c r="J37" s="36" t="str"/>
     </x:row>
@@ -3455,7 +3455,7 @@
         <x:v>TGT-02~05</x:v>
       </x:c>
       <x:c r="G20" s="36" t="str">
-        <x:v>HIS_GENERAL_CHECKUP_COMPLETIONS</x:v>
+        <x:v>완료이력</x:v>
       </x:c>
       <x:c r="H20" s="36" t="str">
         <x:v>현재 Work 상태와 별도</x:v>
@@ -3481,7 +3481,7 @@
         <x:v>NEX-03</x:v>
       </x:c>
       <x:c r="G21" s="36" t="str">
-        <x:v>INFO_PATIENT_EXAM_EXCLUSIONS</x:v>
+        <x:v>수검자.HepatitisBExcluded</x:v>
       </x:c>
       <x:c r="H21" s="36" t="str">
         <x:v>미등록=제외 아님</x:v>
@@ -3507,7 +3507,7 @@
         <x:v>NEX-01~07</x:v>
       </x:c>
       <x:c r="G22" s="36" t="str">
-        <x:v>MST_EXAM_ITEMS</x:v>
+        <x:v>검사코드</x:v>
       </x:c>
       <x:c r="H22" s="36" t="str">
         <x:v>관리 UI 없음</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>AEX-01~05</x:v>
       </x:c>
       <x:c r="G23" s="36" t="str">
-        <x:v>MST_EXAM_ITEMS</x:v>
+        <x:v>검사코드</x:v>
       </x:c>
       <x:c r="H23" s="36" t="str">
         <x:v>공통 ExamItemCode</x:v>
@@ -3559,7 +3559,7 @@
         <x:v>HOL-01~05</x:v>
       </x:c>
       <x:c r="G24" s="36" t="str">
-        <x:v>MST_HOLIDAYS</x:v>
+        <x:v>휴무일</x:v>
       </x:c>
       <x:c r="H24" s="36" t="str">
         <x:v>평일1+토요일1 테스트</x:v>
@@ -3992,7 +3992,7 @@
         <x:v>F-COM-005</x:v>
       </x:c>
       <x:c r="E12" s="36" t="str">
-        <x:v>RSV/RCP 모두 슬롯을 점유하고 CNL만 제외한다.</x:v>
+        <x:v>RSV/RCP 모두 슬롯을 점유하고 CNR·CNC만 제외한다.</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
         <x:v>RP-03</x:v>
@@ -4146,7 +4146,7 @@
         <x:v>취소</x:v>
       </x:c>
       <x:c r="C20" s="36" t="str">
-        <x:v>CNL 상태 보존·복원금지</x:v>
+        <x:v>CNR·CNC 상태 보존·복원금지</x:v>
       </x:c>
       <x:c r="D20" s="36" t="str">
         <x:v>F-RSV-003, F-RCP-003, F-COM-001</x:v>
@@ -4330,7 +4330,7 @@
         <x:v>EP-01~02</x:v>
       </x:c>
       <x:c r="E4" s="36" t="str">
-        <x:v>INFO_PATIENTS</x:v>
+        <x:v>수검자</x:v>
       </x:c>
       <x:c r="F4" s="36" t="str">
         <x:v>조회조건 → PatientId</x:v>
@@ -4353,7 +4353,7 @@
         <x:v>EP-02~07, EP-09</x:v>
       </x:c>
       <x:c r="E5" s="36" t="str">
-        <x:v>INFO_PATIENTS, SEQ_HC_CHART_NO</x:v>
+        <x:v>수검자, SEQ_HC_CHART_NO</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
         <x:v>수검자 입력 → PatientId/ChartNo/LastEditDate</x:v>
@@ -4376,7 +4376,7 @@
         <x:v>EP-04, EP-08, CP-06</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>INFO_PATIENTS, INFO_CHECKUP_WORKS</x:v>
+        <x:v>수검자, 예약접수, 변경이력</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
         <x:v>PatientId+LastEditDate → 갱신값</x:v>
@@ -4399,7 +4399,7 @@
         <x:v>RP-01~08</x:v>
       </x:c>
       <x:c r="E7" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, INFO_CHECKUP_WORK_EXAMS + TGT/NEX/AEX/HOL</x:v>
+        <x:v>예약접수, 검사항목 + TGT/NEX/AEX/HOL</x:v>
       </x:c>
       <x:c r="F7" s="36" t="str">
         <x:v>PatientId+일정+AEX7BIT → WorkId/RowVersion</x:v>
@@ -4422,7 +4422,7 @@
         <x:v>RP-09</x:v>
       </x:c>
       <x:c r="E8" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, INFO_CHECKUP_WORK_EXAMS + TGT/NEX/AEX/HOL</x:v>
+        <x:v>예약접수, 검사항목 + TGT/NEX/AEX/HOL</x:v>
       </x:c>
       <x:c r="F8" s="36" t="str">
         <x:v>WorkId+RowVersion+요청값 → 새 RowVersion</x:v>
@@ -4445,10 +4445,10 @@
         <x:v>RP-10, CP-05</x:v>
       </x:c>
       <x:c r="E9" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS</x:v>
+        <x:v>예약접수</x:v>
       </x:c>
       <x:c r="F9" s="36" t="str">
-        <x:v>WorkId+RowVersion → CNL/새 RowVersion</x:v>
+        <x:v>WorkId+RowVersion → CNR/새 RowVersion</x:v>
       </x:c>
       <x:c r="G9" s="36" t="str">
         <x:v>RSV 조건 UPDATE</x:v>
@@ -4468,7 +4468,7 @@
         <x:v>RCP-01~04</x:v>
       </x:c>
       <x:c r="E10" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, INFO_CHECKUP_WORK_EXAMS + HOL/마감</x:v>
+        <x:v>예약접수, 검사항목 + HOL/마감</x:v>
       </x:c>
       <x:c r="F10" s="36" t="str">
         <x:v>WorkId+RowVersion → RCP/새 RowVersion</x:v>
@@ -4491,7 +4491,7 @@
         <x:v>RCP-05</x:v>
       </x:c>
       <x:c r="E11" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, INFO_CHECKUP_WORK_EXAMS + AEX</x:v>
+        <x:v>예약접수, 검사항목 + AEX</x:v>
       </x:c>
       <x:c r="F11" s="36" t="str">
         <x:v>WorkId+RowVersion+AEX7BIT → 새 RowVersion</x:v>
@@ -4514,10 +4514,10 @@
         <x:v>RCP-06, CP-05</x:v>
       </x:c>
       <x:c r="E12" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS</x:v>
+        <x:v>예약접수</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
-        <x:v>WorkId+RowVersion → CNL/새 RowVersion</x:v>
+        <x:v>WorkId+RowVersion → CNC/새 RowVersion</x:v>
       </x:c>
       <x:c r="G12" s="36" t="str">
         <x:v>RCP 조건 UPDATE</x:v>
@@ -4537,7 +4537,7 @@
         <x:v>CP-05</x:v>
       </x:c>
       <x:c r="E13" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, INFO_CHECKUP_WORK_EXAMS, INFO_PATIENTS, MST_EXAM_ITEMS</x:v>
+        <x:v>예약접수, 검사항목, 수검자, 검사코드</x:v>
       </x:c>
       <x:c r="F13" s="36" t="str">
         <x:v>조회조건/WorkId → Work/Detail</x:v>
@@ -4560,7 +4560,7 @@
         <x:v>EP-03, EP-05~08</x:v>
       </x:c>
       <x:c r="E14" s="36" t="str">
-        <x:v>INFO_PATIENTS, INFO_CHECKUP_WORKS</x:v>
+        <x:v>수검자, 예약접수</x:v>
       </x:c>
       <x:c r="F14" s="36" t="str">
         <x:v>정규화 주민번호/ChartNo/PatientId → 판정</x:v>
@@ -4583,7 +4583,7 @@
         <x:v>TGT-01~05</x:v>
       </x:c>
       <x:c r="E15" s="36" t="str">
-        <x:v>INFO_PATIENTS, HIS_GENERAL_CHECKUP_COMPLETIONS</x:v>
+        <x:v>수검자, 완료이력</x:v>
       </x:c>
       <x:c r="F15" s="36" t="str">
         <x:v>PatientId+ReservationDate → 대상판정</x:v>
@@ -4606,7 +4606,7 @@
         <x:v>NEX-01~07, AEX-01~05</x:v>
       </x:c>
       <x:c r="E16" s="36" t="str">
-        <x:v>MST_EXAM_ITEMS, INFO_PATIENT_EXAM_EXCLUSIONS, INFO_CHECKUP_WORK_EXAMS</x:v>
+        <x:v>검사코드, 수검자.HepatitisBExcluded, 검사항목</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
         <x:v>PatientId+ReservationDate+AEX7BIT → 검사집합</x:v>
@@ -4629,7 +4629,7 @@
         <x:v>RP-02~06, HOL</x:v>
       </x:c>
       <x:c r="E17" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, MST_HOLIDAYS</x:v>
+        <x:v>예약접수, 휴무일</x:v>
       </x:c>
       <x:c r="F17" s="36" t="str">
         <x:v>PatientId+Date+Slot+Context → 가능/정원</x:v>
@@ -4652,7 +4652,7 @@
         <x:v>RCP-02~03, HOL</x:v>
       </x:c>
       <x:c r="E18" s="36" t="str">
-        <x:v>INFO_CHECKUP_WORKS, MST_HOLIDAYS</x:v>
+        <x:v>예약접수, 휴무일</x:v>
       </x:c>
       <x:c r="F18" s="36" t="str">
         <x:v>WorkId+DB현재시각 → 가능판정</x:v>
@@ -4675,7 +4675,7 @@
         <x:v>CP-01~04, HOL</x:v>
       </x:c>
       <x:c r="E19" s="36" t="str">
-        <x:v>MST_HOLIDAYS + DB 서버시각</x:v>
+        <x:v>휴무일 + DB 서버시각</x:v>
       </x:c>
       <x:c r="F19" s="36" t="str">
         <x:v>DB현재일/시각 → 업무가능</x:v>
@@ -5063,7 +5063,7 @@
         <x:v>상태전이</x:v>
       </x:c>
       <x:c r="C23" s="36" t="str">
-        <x:v>RSV→RCP, RSV→CNL, RCP→CNL, 복원금지</x:v>
+        <x:v>RSV→RCP, RSV→CNR, RCP→CNC, 복원금지</x:v>
       </x:c>
       <x:c r="D23" s="36" t="str">
         <x:v>No.22,28,32</x:v>

--- a/docs/baseline/02_Function_Definition.xlsx
+++ b/docs/baseline/02_Function_Definition.xlsx
@@ -2810,7 +2810,7 @@
         <x:v>RP-08, RCP-05</x:v>
       </x:c>
       <x:c r="I34" s="36" t="str">
-        <x:v>검사항목</x:v>
+        <x:v>예약접수.추가검사항목</x:v>
       </x:c>
       <x:c r="J34" s="36" t="str"/>
     </x:row>
@@ -4399,13 +4399,13 @@
         <x:v>RP-01~08</x:v>
       </x:c>
       <x:c r="E7" s="36" t="str">
-        <x:v>예약접수, 검사항목 + TGT/NEX/AEX/HOL</x:v>
+        <x:v>예약접수(검사구성) + TGT/NEX/AEX/HOL</x:v>
       </x:c>
       <x:c r="F7" s="36" t="str">
         <x:v>PatientId+일정+AEX7BIT → WorkId/RowVersion</x:v>
       </x:c>
       <x:c r="G7" s="36" t="str">
-        <x:v>Work Aggregate Transaction</x:v>
+        <x:v>Work 1행 Transaction</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" hidden="0" customHeight="1">
@@ -4422,7 +4422,7 @@
         <x:v>RP-09</x:v>
       </x:c>
       <x:c r="E8" s="36" t="str">
-        <x:v>예약접수, 검사항목 + TGT/NEX/AEX/HOL</x:v>
+        <x:v>예약접수(검사구성) + TGT/NEX/AEX/HOL</x:v>
       </x:c>
       <x:c r="F8" s="36" t="str">
         <x:v>WorkId+RowVersion+요청값 → 새 RowVersion</x:v>
@@ -4468,7 +4468,7 @@
         <x:v>RCP-01~04</x:v>
       </x:c>
       <x:c r="E10" s="36" t="str">
-        <x:v>예약접수, 검사항목 + HOL/마감</x:v>
+        <x:v>예약접수(검사구성) + HOL/마감</x:v>
       </x:c>
       <x:c r="F10" s="36" t="str">
         <x:v>WorkId+RowVersion → RCP/새 RowVersion</x:v>
@@ -4491,7 +4491,7 @@
         <x:v>RCP-05</x:v>
       </x:c>
       <x:c r="E11" s="36" t="str">
-        <x:v>예약접수, 검사항목 + AEX</x:v>
+        <x:v>예약접수(검사구성) + AEX</x:v>
       </x:c>
       <x:c r="F11" s="36" t="str">
         <x:v>WorkId+RowVersion+AEX7BIT → 새 RowVersion</x:v>
@@ -4537,10 +4537,10 @@
         <x:v>CP-05</x:v>
       </x:c>
       <x:c r="E13" s="36" t="str">
-        <x:v>예약접수, 검사항목, 수검자, 검사코드</x:v>
+        <x:v>예약접수(검사구성), 수검자, 검사코드</x:v>
       </x:c>
       <x:c r="F13" s="36" t="str">
-        <x:v>조회조건/WorkId → Work/Detail</x:v>
+        <x:v>조회조건/WorkId → Work + 검사구성</x:v>
       </x:c>
       <x:c r="G13" s="36" t="str">
         <x:v>공통 Workbench</x:v>
@@ -4606,13 +4606,13 @@
         <x:v>NEX-01~07, AEX-01~05</x:v>
       </x:c>
       <x:c r="E16" s="36" t="str">
-        <x:v>검사코드, 수검자.HepatitisBExcluded, 검사항목</x:v>
+        <x:v>검사코드, 수검자.B형간염제외여부, 예약접수(검사구성)</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
         <x:v>PatientId+ReservationDate+AEX7BIT → 검사집합</x:v>
       </x:c>
       <x:c r="G16" s="36" t="str">
-        <x:v>NEX 실제 8~11행 / EX012 공통코드 중복차단</x:v>
+        <x:v>NEX 실제 8~11종 / EX012 공통코드 중복차단</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="44" hidden="0" customHeight="1">

--- a/docs/baseline/02_Function_Definition.xlsx
+++ b/docs/baseline/02_Function_Definition.xlsx
@@ -267,7 +267,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FunctionDefinitionTable" displayName="FunctionDefinitionTable" ref="A3:I39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FunctionDefinitionTable" displayName="FunctionDefinitionTable" ref="A3:I40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="No"/>
     <x:tableColumn id="2" name="기능 ID"/>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DbTraceTable" displayName="DbTraceTable" ref="A3:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DbTraceTable" displayName="DbTraceTable" ref="A3:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Function ID"/>
     <x:tableColumn id="2" name="기능명"/>
@@ -629,7 +629,7 @@
         <x:v>기능 정의</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:v>16개 Function ID / 36개 기능행</x:v>
+        <x:v>17개 Function ID / 37개 기능행</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" hidden="0" customHeight="1">
@@ -689,7 +689,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>기능 정의 — 16개 Function ID / 36개 기능행</x:v>
+        <x:v>기능 정의 — 17개 Function ID / 37개 기능행</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -1771,6 +1771,35 @@
       </x:c>
       <x:c r="I39" s="36" t="str">
         <x:v>CP-01~04, HOL-01~05, 마감시간 정책</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="46" hidden="0" customHeight="1">
+      <x:c r="A40" s="52" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B40" s="50" t="str">
+        <x:v>F-COM-008</x:v>
+      </x:c>
+      <x:c r="C40" s="50" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="D40" s="36" t="str">
+        <x:v>변경기록</x:v>
+      </x:c>
+      <x:c r="E40" s="36" t="str">
+        <x:v>변경기록 열람</x:v>
+      </x:c>
+      <x:c r="F40" s="36" t="str">
+        <x:v>대상 행 단위 조회</x:v>
+      </x:c>
+      <x:c r="G40" s="36" t="str">
+        <x:v>수검자·예약접수 한 행의 변경기록을 기록일시 최신순으로 열람한다. 편집·삭제·복원은 제공하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H40" s="36" t="str">
+        <x:v>P01~P03 전체</x:v>
+      </x:c>
+      <x:c r="I40" s="36" t="str">
+        <x:v>CP-06</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4684,6 +4713,29 @@
         <x:v>DATEFIRST 비종속</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="44" hidden="0" customHeight="1">
+      <x:c r="A20" s="50" t="str">
+        <x:v>F-COM-008</x:v>
+      </x:c>
+      <x:c r="B20" s="36" t="str">
+        <x:v>변경기록 열람</x:v>
+      </x:c>
+      <x:c r="C20" s="36" t="str">
+        <x:v>P01~P03</x:v>
+      </x:c>
+      <x:c r="D20" s="36" t="str">
+        <x:v>CP-06</x:v>
+      </x:c>
+      <x:c r="E20" s="36" t="str">
+        <x:v>변경이력</x:v>
+      </x:c>
+      <x:c r="F20" s="36" t="str">
+        <x:v>TargetTable/TargetKey → 변경기록 목록</x:v>
+      </x:c>
+      <x:c r="G20" s="36" t="str">
+        <x:v>읽기 전용. 기록 0건도 정상</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -5131,7 +5183,7 @@
         <x:v>DB Entity 추적</x:v>
       </x:c>
       <x:c r="C27" s="36" t="str">
-        <x:v>16 Function ID→7 Table/Rule Object</x:v>
+        <x:v>17 Function ID→7 Table/Rule Object</x:v>
       </x:c>
       <x:c r="D27" s="36" t="str">
         <x:v>16/16</x:v>
@@ -5185,7 +5237,7 @@
         <x:v>수검자3+예약3+접수3+공통7</x:v>
       </x:c>
       <x:c r="D30" s="36" t="str">
-        <x:v>16개 Function ID</x:v>
+        <x:v>17개 Function ID</x:v>
       </x:c>
       <x:c r="E30" s="36" t="str">
         <x:v>PASS</x:v>

--- a/docs/baseline/02_Function_Definition.xlsx
+++ b/docs/baseline/02_Function_Definition.xlsx
@@ -267,7 +267,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FunctionDefinitionTable" displayName="FunctionDefinitionTable" ref="A3:I40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FunctionDefinitionTable" displayName="FunctionDefinitionTable" ref="A3:I41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="No"/>
     <x:tableColumn id="2" name="기능 ID"/>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BusinessRuleTable" displayName="BusinessRuleTable" ref="A3:J39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BusinessRuleTable" displayName="BusinessRuleTable" ref="A3:J40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Rule Group"/>
     <x:tableColumn id="2" name="Rule / Code"/>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DbTraceTable" displayName="DbTraceTable" ref="A3:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DbTraceTable" displayName="DbTraceTable" ref="A3:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Function ID"/>
     <x:tableColumn id="2" name="기능명"/>
@@ -589,7 +589,7 @@
         <x:v>문서 버전</x:v>
       </x:c>
       <x:c r="F3" s="23" t="str">
-        <x:v>v2.0</x:v>
+        <x:v>v2.1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" hidden="0" customHeight="1">
@@ -597,19 +597,19 @@
         <x:v>기준일</x:v>
       </x:c>
       <x:c r="B4" s="23" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
         <x:v>기준선 ID</x:v>
       </x:c>
       <x:c r="D4" s="23" t="str">
-        <x:v>HC-RSV-RCP-20260904-R3</x:v>
+        <x:v>HC-RSV-RCP-20260908-R7</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
         <x:v>논리 기능</x:v>
       </x:c>
       <x:c r="F4" s="23" t="str">
-        <x:v>수검자 3 / 예약 3 / 접수 3 / 공통 7</x:v>
+        <x:v>수검자 3 / 예약 3 / 접수 3 / 공통 9</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" hidden="0" customHeight="1">
@@ -629,7 +629,7 @@
         <x:v>기능 정의</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:v>17개 Function ID / 37개 기능행</x:v>
+        <x:v>18개 Function ID / 38개 기능행</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" hidden="0" customHeight="1">
@@ -643,19 +643,19 @@
         <x:v>Rule</x:v>
       </x:c>
       <x:c r="D6" s="23" t="str">
-        <x:v>TGT 5 / NEX 7 / AEX 5 / HOL 5</x:v>
+        <x:v>TGT 5 / NEX 7 / AEX 5 / HOL 6</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
         <x:v>변경 통제</x:v>
       </x:c>
       <x:c r="F6" s="23" t="str">
-        <x:v>본 기준일 이후 본 파일은 수정하지 않으며 후속 Phase는 이 계약을 구현한다.</x:v>
+        <x:v>본 파일의 개정은 재봉인 절차로만 하며 후속 Phase는 이 계약을 구현한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1"/>
     <x:row r="8" ht="34" hidden="0" customHeight="1">
       <x:c r="A8" s="30" t="str">
-        <x:v>최종 판정: 정책 ↔ 프로세스 ↔ 기능 ↔ Rule ↔ UI ↔ DB 추적에 구조적 결함이 없으며, 본 파일은 HC-RSV-RCP-20260904-R3 기준선의 최종 기능계약으로 이후 READ-ONLY로 사용한다.</x:v>
+        <x:v>최종 판정: 정책 ↔ 프로세스 ↔ 기능 ↔ Rule ↔ UI ↔ DB 추적에 구조적 결함이 없으며, 본 파일은 HC-RSV-RCP-20260908-R7 기준선의 최종 기능계약으로 이후 READ-ONLY로 사용한다.</x:v>
       </x:c>
       <x:c r="B8" s="30"/>
       <x:c r="C8" s="30"/>
@@ -1074,7 +1074,7 @@
         <x:v>P02-03~04</x:v>
       </x:c>
       <x:c r="I15" s="36" t="str">
-        <x:v>CP-01~04, HOL-01~05, RP-02~06, 마감시간 정책</x:v>
+        <x:v>CP-01~04, HOL-01~06, RP-02~06, 마감시간 정책</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="46" hidden="0" customHeight="1">
@@ -1277,7 +1277,7 @@
         <x:v>P02-06, P02-03~04</x:v>
       </x:c>
       <x:c r="I22" s="36" t="str">
-        <x:v>RP-02~09, TGT-01~05, NEX-01~07, AEX-01~05, HOL-01~05</x:v>
+        <x:v>RP-02~09, TGT-01~05, NEX-01~07, AEX-01~05, HOL-01~06</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="46" hidden="0" customHeight="1">
@@ -1509,7 +1509,7 @@
         <x:v>P03-03</x:v>
       </x:c>
       <x:c r="I30" s="36" t="str">
-        <x:v>CP-01~04, HOL-01~05, RCP-02~03, 마감시간 정책</x:v>
+        <x:v>CP-01~04, HOL-01~06, RCP-02~03, 마감시간 정책</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="46" hidden="0" customHeight="1">
@@ -1770,7 +1770,7 @@
         <x:v>P01~P03 전체</x:v>
       </x:c>
       <x:c r="I39" s="36" t="str">
-        <x:v>CP-01~04, HOL-01~05, 마감시간 정책</x:v>
+        <x:v>CP-01~04, HOL-01~06, 마감시간 정책</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="46" hidden="0" customHeight="1">
@@ -1800,6 +1800,35 @@
       </x:c>
       <x:c r="I40" s="36" t="str">
         <x:v>CP-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="46" hidden="0" customHeight="1">
+      <x:c r="A41" s="52" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B41" s="50" t="str">
+        <x:v>F-COM-009</x:v>
+      </x:c>
+      <x:c r="C41" s="50" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="D41" s="36" t="str">
+        <x:v>기준정보</x:v>
+      </x:c>
+      <x:c r="E41" s="36" t="str">
+        <x:v>휴무일 관리</x:v>
+      </x:c>
+      <x:c r="F41" s="36" t="str">
+        <x:v>자체휴무일 등록·수정·삭제</x:v>
+      </x:c>
+      <x:c r="G41" s="36" t="str">
+        <x:v>휴무일 Master를 기간·구분으로 열람하고 자체휴무일을 등록·수정·삭제한다. 법정공휴일·대체공휴일은 Seed Data로 제공하며 화면에서 바꾸지 않는다.</x:v>
+      </x:c>
+      <x:c r="H41" s="36" t="str">
+        <x:v>해당 없음 (기준정보)</x:v>
+      </x:c>
+      <x:c r="I41" s="36" t="str">
+        <x:v>HOL-03~06</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2919,7 +2948,7 @@
         <x:v>업무 가능일</x:v>
       </x:c>
       <x:c r="E37" s="36" t="str">
-        <x:v>공휴일 API·외부 달력은 사용하지 않고 공휴일과 센터 휴진일을 동일 Master로 관리한다.</x:v>
+        <x:v>공휴일 API·외부 달력은 사용하지 않고 법정공휴일·대체공휴일·센터 자체 휴무일을 동일 Master로 관리하며 휴무구분으로 구별한다.</x:v>
       </x:c>
       <x:c r="F37" s="36" t="str">
         <x:v>F-COM-005~007</x:v>
@@ -2949,7 +2978,7 @@
         <x:v>업무 가능일</x:v>
       </x:c>
       <x:c r="E38" s="36" t="str">
-        <x:v>최소정보는 휴무일·휴무일명·사용여부·비고이며 동일 날짜 중복을 허용하지 않는다.</x:v>
+        <x:v>최소정보는 휴무일·휴무일명·휴무구분·사용여부·비고이며 동일 날짜 중복을 허용하지 않는다.</x:v>
       </x:c>
       <x:c r="F38" s="36" t="str">
         <x:v>F-COM-005~007</x:v>
@@ -2979,10 +3008,10 @@
         <x:v>업무 가능일</x:v>
       </x:c>
       <x:c r="E39" s="36" t="str">
-        <x:v>관리 UI 없이 DB Master/Seed Data로 제공하고 평일 1건·토요일 1건의 테스트 휴무일을 준비한다.</x:v>
+        <x:v>자체휴무일은 관리 화면에서 등록·수정·삭제하고 법정공휴일·대체공휴일은 Seed Data로 제공한다.</x:v>
       </x:c>
       <x:c r="F39" s="36" t="str">
-        <x:v>F-COM-005~007</x:v>
+        <x:v>F-COM-005~007, F-COM-009</x:v>
       </x:c>
       <x:c r="G39" s="36" t="str">
         <x:v>P01~P03</x:v>
@@ -2994,6 +3023,36 @@
         <x:v>Seed Data</x:v>
       </x:c>
       <x:c r="J39" s="36" t="str"/>
+    </x:row>
+    <x:row r="40" ht="46" hidden="0" customHeight="1">
+      <x:c r="A40" s="50" t="str">
+        <x:v>HOL</x:v>
+      </x:c>
+      <x:c r="B40" s="50" t="str">
+        <x:v>HOL-06</x:v>
+      </x:c>
+      <x:c r="C40" s="50" t="str">
+        <x:v>갱신</x:v>
+      </x:c>
+      <x:c r="D40" s="50" t="str">
+        <x:v>업무 가능일</x:v>
+      </x:c>
+      <x:c r="E40" s="36" t="str">
+        <x:v>공휴일 Seed Data는 유한 기간만 등재하고 만료 전 갱신은 운영 책임이며 잔여가 임계 미만이면 경고한다.</x:v>
+      </x:c>
+      <x:c r="F40" s="36" t="str">
+        <x:v>F-COM-009</x:v>
+      </x:c>
+      <x:c r="G40" s="36" t="str">
+        <x:v>P01~P03</x:v>
+      </x:c>
+      <x:c r="H40" s="36" t="str">
+        <x:v>CP-03</x:v>
+      </x:c>
+      <x:c r="I40" s="36" t="str">
+        <x:v>Seed Data</x:v>
+      </x:c>
+      <x:c r="J40" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3579,19 +3638,19 @@
         <x:v>휴무일</x:v>
       </x:c>
       <x:c r="D24" s="36" t="str">
-        <x:v>HOL 업무 가능일 판정</x:v>
+        <x:v>HOL 업무 가능일 판정 · 자체휴무일 CRUD</x:v>
       </x:c>
       <x:c r="E24" s="36" t="str">
-        <x:v>DB Master/Seed</x:v>
+        <x:v>DB Master/Seed + 관리 화면</x:v>
       </x:c>
       <x:c r="F24" s="36" t="str">
-        <x:v>HOL-01~05</x:v>
+        <x:v>HOL-01~06</x:v>
       </x:c>
       <x:c r="G24" s="36" t="str">
         <x:v>휴무일</x:v>
       </x:c>
       <x:c r="H24" s="36" t="str">
-        <x:v>평일1+토요일1 테스트</x:v>
+        <x:v>공휴일 2년치 · 자체휴무일 화면 편집</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="40" hidden="0" customHeight="1">
@@ -3722,10 +3781,10 @@
         <x:v>관리</x:v>
       </x:c>
       <x:c r="C30" s="36" t="str">
-        <x:v>휴무일·검사·AEX 관리자 CRUD</x:v>
+        <x:v>검사·AEX 관리자 CRUD</x:v>
       </x:c>
       <x:c r="D30" s="36" t="str">
-        <x:v>필요 데이터는 DB Seed로 제공</x:v>
+        <x:v>법정·대체 공휴일은 DB Seed로 제공</x:v>
       </x:c>
       <x:c r="E30" s="36" t="str">
         <x:v>구현 제외</x:v>
@@ -4095,16 +4154,16 @@
         <x:v>휴무일</x:v>
       </x:c>
       <x:c r="C16" s="36" t="str">
-        <x:v>월~토+활성 HOL Master</x:v>
+        <x:v>월~토 + 활성 HOL Master (휴무구분 1테이블)</x:v>
       </x:c>
       <x:c r="D16" s="36" t="str">
-        <x:v>F-COM-005~007</x:v>
+        <x:v>F-COM-005~007, F-COM-009</x:v>
       </x:c>
       <x:c r="E16" s="36" t="str">
-        <x:v>외부 API 없이 공휴일과 센터 휴진일을 동일 방식으로 처리한다.</x:v>
+        <x:v>외부 API 없이 법정·대체 공휴일과 자체 휴무일을 한 Master에서 휴무구분으로 구별해 처리한다.</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
-        <x:v>HOL-01~05</x:v>
+        <x:v>HOL-01~06</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="44" hidden="0" customHeight="1">
@@ -4385,7 +4444,7 @@
         <x:v>수검자, SEQ_HC_CHART_NO</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
-        <x:v>수검자 입력 → PatientId/ChartNo/LastEditDate</x:v>
+        <x:v>수검자 입력 → PatientId/ChartNo/RowVersion</x:v>
       </x:c>
       <x:c r="G5" s="36" t="str">
         <x:v>수검자 단일행 Transaction</x:v>
@@ -4408,7 +4467,7 @@
         <x:v>수검자, 예약접수, 변경이력</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>PatientId+LastEditDate → 갱신값</x:v>
+        <x:v>PatientId+RowVersion → 갱신값</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str">
         <x:v>Patient 단위 직렬화</x:v>
@@ -4734,6 +4793,29 @@
       </x:c>
       <x:c r="G20" s="36" t="str">
         <x:v>읽기 전용. 기록 0건도 정상</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="44" hidden="0" customHeight="1">
+      <x:c r="A21" s="50" t="str">
+        <x:v>F-COM-009</x:v>
+      </x:c>
+      <x:c r="B21" s="36" t="str">
+        <x:v>휴무일 관리</x:v>
+      </x:c>
+      <x:c r="C21" s="36" t="str">
+        <x:v>기준정보</x:v>
+      </x:c>
+      <x:c r="D21" s="36" t="str">
+        <x:v>HOL-03~06</x:v>
+      </x:c>
+      <x:c r="E21" s="36" t="str">
+        <x:v>휴무일</x:v>
+      </x:c>
+      <x:c r="F21" s="36" t="str">
+        <x:v>기간+구분 → 목록 / 자체휴무일 등록·수정·삭제</x:v>
+      </x:c>
+      <x:c r="G21" s="36" t="str">
+        <x:v>법정·대체 공휴일은 읽기 전용</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4979,10 +5061,10 @@
         <x:v>HOL Rule</x:v>
       </x:c>
       <x:c r="C15" s="36" t="str">
-        <x:v>HOL-01~HOL-05</x:v>
+        <x:v>HOL-01~HOL-06</x:v>
       </x:c>
       <x:c r="D15" s="36" t="str">
-        <x:v>5/5 기능·Process 추적</x:v>
+        <x:v>6/6 기능·Process 추적</x:v>
       </x:c>
       <x:c r="E15" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5183,10 +5265,10 @@
         <x:v>DB Entity 추적</x:v>
       </x:c>
       <x:c r="C27" s="36" t="str">
-        <x:v>17 Function ID→7 Table/Rule Object</x:v>
+        <x:v>18 Function ID→7 Table/Rule Object</x:v>
       </x:c>
       <x:c r="D27" s="36" t="str">
-        <x:v>16/16</x:v>
+        <x:v>18/18</x:v>
       </x:c>
       <x:c r="E27" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5234,10 +5316,10 @@
         <x:v>논리 기능 수</x:v>
       </x:c>
       <x:c r="C30" s="36" t="str">
-        <x:v>수검자3+예약3+접수3+공통7</x:v>
+        <x:v>수검자3+예약3+접수3+공통9</x:v>
       </x:c>
       <x:c r="D30" s="36" t="str">
-        <x:v>17개 Function ID</x:v>
+        <x:v>18개 Function ID</x:v>
       </x:c>
       <x:c r="E30" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5254,7 +5336,7 @@
         <x:v>정규화 기능행</x:v>
       </x:c>
       <x:c r="D31" s="36" t="str">
-        <x:v>36개</x:v>
+        <x:v>38개</x:v>
       </x:c>
       <x:c r="E31" s="36" t="str">
         <x:v>PASS</x:v>
